--- a/Deliverables/BOM/(5-100 Boards)Trustedparts-BOM.xlsx
+++ b/Deliverables/BOM/(5-100 Boards)Trustedparts-BOM.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\SH-Sound-Board\Deliverables\BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6069C359-F7D1-4481-A72F-8D39F881FF6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9968A76B-5502-4D68-81FC-FFB2A3F7774D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-10110" yWindow="4155" windowWidth="21600" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="52">
   <si>
     <t>S. No.</t>
   </si>
@@ -183,6 +183,9 @@
   </si>
   <si>
     <t>----</t>
+  </si>
+  <si>
+    <t>Digikey</t>
   </si>
 </sst>
 </file>
@@ -192,7 +195,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.0000_);[Red]\(&quot;$&quot;#,##0.0000\)"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -245,14 +248,6 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <u/>
-      <sz val="10"/>
-      <color rgb="FF0000FF"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -274,7 +269,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="22">
+  <borders count="23">
     <border>
       <left/>
       <right/>
@@ -561,6 +556,19 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -616,9 +624,6 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -648,18 +653,6 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -670,12 +663,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -689,9 +676,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
@@ -715,10 +699,34 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="22" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1003,9 +1011,9 @@
     <col min="1" max="1" width="6.140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="13.140625" customWidth="1"/>
     <col min="3" max="3" width="60.85546875" customWidth="1"/>
-    <col min="4" max="4" width="21.28515625" style="31" customWidth="1"/>
-    <col min="5" max="5" width="20" style="31" customWidth="1"/>
-    <col min="6" max="6" width="27.28515625" style="31" customWidth="1"/>
+    <col min="4" max="4" width="21.28515625" style="26" customWidth="1"/>
+    <col min="5" max="5" width="20" style="26" customWidth="1"/>
+    <col min="6" max="6" width="27.28515625" style="26" customWidth="1"/>
     <col min="7" max="7" width="14.140625" customWidth="1"/>
     <col min="8" max="8" width="17.28515625" customWidth="1"/>
     <col min="9" max="9" width="14.42578125" customWidth="1"/>
@@ -1023,28 +1031,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:20" ht="15.75">
-      <c r="A1" s="26" t="s">
+      <c r="A1" s="44" t="s">
         <v>36</v>
       </c>
-      <c r="B1" s="27"/>
-      <c r="C1" s="27"/>
-      <c r="D1" s="27"/>
-      <c r="E1" s="27"/>
-      <c r="F1" s="27"/>
-      <c r="G1" s="27"/>
-      <c r="H1" s="27"/>
-      <c r="I1" s="27"/>
-      <c r="J1" s="27"/>
-      <c r="K1" s="27"/>
-      <c r="L1" s="27"/>
-      <c r="M1" s="27"/>
-      <c r="N1" s="27"/>
-      <c r="O1" s="27"/>
-      <c r="P1" s="27"/>
-      <c r="Q1" s="27"/>
-      <c r="R1" s="27"/>
-      <c r="S1" s="27"/>
-      <c r="T1" s="28"/>
+      <c r="B1" s="45"/>
+      <c r="C1" s="45"/>
+      <c r="D1" s="45"/>
+      <c r="E1" s="45"/>
+      <c r="F1" s="45"/>
+      <c r="G1" s="45"/>
+      <c r="H1" s="45"/>
+      <c r="I1" s="45"/>
+      <c r="J1" s="45"/>
+      <c r="K1" s="45"/>
+      <c r="L1" s="45"/>
+      <c r="M1" s="45"/>
+      <c r="N1" s="45"/>
+      <c r="O1" s="45"/>
+      <c r="P1" s="45"/>
+      <c r="Q1" s="45"/>
+      <c r="R1" s="45"/>
+      <c r="S1" s="45"/>
+      <c r="T1" s="46"/>
     </row>
     <row r="2" spans="1:20" ht="15.75" thickBot="1">
       <c r="A2" s="1" t="s">
@@ -1115,89 +1123,89 @@
       <c r="B3" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="C3" s="48" t="s">
+      <c r="C3" s="40" t="s">
         <v>33</v>
       </c>
-      <c r="D3" s="36" t="s">
+      <c r="D3" s="29" t="s">
         <v>34</v>
       </c>
-      <c r="E3" s="36" t="s">
+      <c r="E3" s="29" t="s">
         <v>16</v>
       </c>
-      <c r="F3" s="37" t="s">
+      <c r="F3" s="30" t="s">
         <v>35</v>
       </c>
-      <c r="G3" s="49" t="s">
+      <c r="G3" s="41" t="s">
         <v>45</v>
       </c>
-      <c r="H3" s="22" t="s">
+      <c r="H3" s="21" t="s">
         <v>38</v>
       </c>
-      <c r="I3" s="22" t="s">
+      <c r="I3" s="21" t="s">
         <v>48</v>
       </c>
-      <c r="J3" s="23">
+      <c r="J3" s="22">
         <v>1</v>
       </c>
-      <c r="K3" s="24">
+      <c r="K3" s="23">
         <f>J3*5</f>
         <v>5</v>
       </c>
-      <c r="L3" s="24">
+      <c r="L3" s="23">
         <f>J3*100</f>
         <v>100</v>
       </c>
-      <c r="M3" s="24">
+      <c r="M3" s="23">
         <v>100</v>
       </c>
-      <c r="N3" s="24">
+      <c r="N3" s="23">
         <v>100</v>
       </c>
-      <c r="O3" s="39" t="s">
+      <c r="O3" s="32" t="s">
         <v>46</v>
       </c>
-      <c r="P3" s="38">
+      <c r="P3" s="31">
         <v>0.19800000000000001</v>
       </c>
-      <c r="Q3" s="38">
+      <c r="Q3" s="31">
         <f>P3*M3</f>
         <v>19.8</v>
       </c>
-      <c r="R3" s="38">
+      <c r="R3" s="31">
         <v>0.19800000000000001</v>
       </c>
-      <c r="S3" s="38">
+      <c r="S3" s="31">
         <f>R3*N3</f>
         <v>19.8</v>
       </c>
-      <c r="T3" s="25"/>
+      <c r="T3" s="24"/>
     </row>
     <row r="4" spans="1:20" ht="30.75" thickBot="1">
       <c r="A4" s="3">
         <v>2</v>
       </c>
-      <c r="B4" s="40" t="s">
+      <c r="B4" s="47" t="s">
         <v>21</v>
       </c>
-      <c r="C4" s="46" t="s">
+      <c r="C4" s="38" t="s">
         <v>22</v>
       </c>
-      <c r="D4" s="41" t="s">
+      <c r="D4" s="33" t="s">
         <v>18</v>
       </c>
-      <c r="E4" s="41" t="s">
+      <c r="E4" s="33" t="s">
         <v>16</v>
       </c>
-      <c r="F4" s="41" t="s">
+      <c r="F4" s="33" t="s">
         <v>23</v>
       </c>
       <c r="G4" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="H4" s="7" t="s">
+      <c r="H4" s="51" t="s">
         <v>15</v>
       </c>
-      <c r="I4" s="7" t="s">
+      <c r="I4" s="51" t="s">
         <v>38</v>
       </c>
       <c r="J4" s="8">
@@ -1217,7 +1225,7 @@
       <c r="N4" s="9">
         <v>100</v>
       </c>
-      <c r="O4" s="42" t="s">
+      <c r="O4" s="34" t="s">
         <v>40</v>
       </c>
       <c r="P4" s="10">
@@ -1240,26 +1248,26 @@
       <c r="A5" s="3">
         <v>3</v>
       </c>
-      <c r="B5" s="33"/>
-      <c r="C5" s="45" t="s">
+      <c r="B5" s="48"/>
+      <c r="C5" s="37" t="s">
         <v>24</v>
       </c>
-      <c r="D5" s="32" t="s">
+      <c r="D5" s="27" t="s">
         <v>25</v>
       </c>
-      <c r="E5" s="32" t="s">
+      <c r="E5" s="27" t="s">
         <v>16</v>
       </c>
-      <c r="F5" s="30" t="s">
+      <c r="F5" s="25" t="s">
         <v>26</v>
       </c>
       <c r="G5" s="12" t="s">
         <v>49</v>
       </c>
-      <c r="H5" s="7" t="s">
+      <c r="H5" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="I5" s="7" t="s">
+      <c r="I5" s="12" t="s">
         <v>15</v>
       </c>
       <c r="J5" s="13">
@@ -1273,40 +1281,46 @@
         <f t="shared" ref="L5:L7" si="1">J5*100</f>
         <v>100</v>
       </c>
-      <c r="M5" s="51" t="s">
+      <c r="M5" s="42" t="s">
         <v>50</v>
       </c>
-      <c r="N5" s="51" t="s">
+      <c r="N5" s="42" t="s">
         <v>50</v>
       </c>
-      <c r="O5" s="15"/>
-      <c r="P5" s="16"/>
-      <c r="Q5" s="16" t="e">
-        <f t="shared" ref="Q5:Q6" si="2">P5*M5</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="R5" s="16"/>
-      <c r="S5" s="16" t="e">
-        <f t="shared" ref="S5:S6" si="3">R5*N5</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="T5" s="17"/>
+      <c r="O5" s="28" t="s">
+        <v>51</v>
+      </c>
+      <c r="P5" s="15">
+        <v>1.47</v>
+      </c>
+      <c r="Q5" s="15">
+        <f>P5*K5</f>
+        <v>7.35</v>
+      </c>
+      <c r="R5" s="15">
+        <v>1.03738</v>
+      </c>
+      <c r="S5" s="15">
+        <f>R5*L5</f>
+        <v>103.738</v>
+      </c>
+      <c r="T5" s="16"/>
     </row>
     <row r="6" spans="1:20" ht="15.75" thickBot="1">
       <c r="A6" s="3">
         <v>4</v>
       </c>
-      <c r="B6" s="33"/>
-      <c r="C6" s="45" t="s">
+      <c r="B6" s="48"/>
+      <c r="C6" s="37" t="s">
         <v>27</v>
       </c>
-      <c r="D6" s="32" t="s">
+      <c r="D6" s="27" t="s">
         <v>28</v>
       </c>
-      <c r="E6" s="32" t="s">
+      <c r="E6" s="27" t="s">
         <v>16</v>
       </c>
-      <c r="F6" s="30" t="s">
+      <c r="F6" s="25" t="s">
         <v>29</v>
       </c>
       <c r="G6" s="12" t="s">
@@ -1335,84 +1349,84 @@
       <c r="N6" s="14">
         <v>200</v>
       </c>
-      <c r="O6" s="35" t="s">
+      <c r="O6" s="28" t="s">
         <v>40</v>
       </c>
-      <c r="P6" s="16">
+      <c r="P6" s="15">
         <v>4.7100000000000003E-2</v>
       </c>
-      <c r="Q6" s="16">
-        <f t="shared" si="2"/>
+      <c r="Q6" s="15">
+        <f t="shared" ref="Q5:Q6" si="2">P6*M6</f>
         <v>0.47100000000000003</v>
       </c>
-      <c r="R6" s="16">
+      <c r="R6" s="15">
         <v>3.8199999999999998E-2</v>
       </c>
-      <c r="S6" s="16">
-        <f t="shared" si="3"/>
+      <c r="S6" s="15">
+        <f t="shared" ref="S5:S6" si="3">R6*N6</f>
         <v>7.64</v>
       </c>
-      <c r="T6" s="17"/>
+      <c r="T6" s="16"/>
     </row>
     <row r="7" spans="1:20" ht="15.75" thickBot="1">
-      <c r="A7" s="1">
+      <c r="A7" s="3">
         <v>5</v>
       </c>
-      <c r="B7" s="34"/>
-      <c r="C7" s="47" t="s">
+      <c r="B7" s="49"/>
+      <c r="C7" s="39" t="s">
         <v>30</v>
       </c>
-      <c r="D7" s="43" t="s">
+      <c r="D7" s="35" t="s">
         <v>31</v>
       </c>
-      <c r="E7" s="43" t="s">
+      <c r="E7" s="35" t="s">
         <v>16</v>
       </c>
-      <c r="F7" s="44" t="s">
+      <c r="F7" s="36" t="s">
         <v>32</v>
       </c>
-      <c r="G7" s="18" t="s">
+      <c r="G7" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="H7" s="18" t="s">
+      <c r="H7" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="I7" s="18" t="s">
+      <c r="I7" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="J7" s="19">
+      <c r="J7" s="18">
         <v>1</v>
       </c>
-      <c r="K7" s="20">
+      <c r="K7" s="19">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="L7" s="20">
+      <c r="L7" s="19">
         <f t="shared" si="1"/>
         <v>100</v>
       </c>
-      <c r="M7" s="18" t="s">
+      <c r="M7" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="N7" s="18" t="s">
+      <c r="N7" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="O7" s="18" t="s">
+      <c r="O7" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="P7" s="18" t="s">
+      <c r="P7" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="Q7" s="18" t="s">
+      <c r="Q7" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="R7" s="18" t="s">
+      <c r="R7" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="S7" s="18" t="s">
+      <c r="S7" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="T7" s="21"/>
+      <c r="T7" s="20"/>
     </row>
     <row r="8" spans="1:20" ht="19.5" thickBot="1">
       <c r="J8" s="50" t="s">
@@ -1422,32 +1436,32 @@
       <c r="L8" s="50"/>
       <c r="M8" s="50"/>
       <c r="N8" s="50"/>
-      <c r="Q8" s="6" t="e">
+      <c r="Q8" s="6">
         <f>SUM(Q3:Q7)</f>
-        <v>#VALUE!</v>
+        <v>28.245000000000001</v>
       </c>
       <c r="R8" s="6"/>
-      <c r="S8" s="6" t="e">
+      <c r="S8" s="6">
         <f>SUM(S3:S7)</f>
-        <v>#VALUE!</v>
+        <v>141.30799999999999</v>
       </c>
     </row>
     <row r="9" spans="1:20" ht="18.75">
-      <c r="J9" s="29" t="s">
+      <c r="J9" s="43" t="s">
         <v>20</v>
       </c>
-      <c r="K9" s="29"/>
-      <c r="L9" s="29"/>
-      <c r="M9" s="29"/>
-      <c r="N9" s="29"/>
-      <c r="Q9" s="6" t="e">
+      <c r="K9" s="43"/>
+      <c r="L9" s="43"/>
+      <c r="M9" s="43"/>
+      <c r="N9" s="43"/>
+      <c r="Q9" s="6">
         <f>Q8/5</f>
-        <v>#VALUE!</v>
+        <v>5.649</v>
       </c>
       <c r="R9" s="6"/>
-      <c r="S9" s="6" t="e">
+      <c r="S9" s="6">
         <f>S8/100</f>
-        <v>#VALUE!</v>
+        <v>1.4130799999999999</v>
       </c>
     </row>
   </sheetData>
@@ -1501,9 +1515,10 @@
     <hyperlink ref="O4" r:id="rId1" xr:uid="{C4B44CEF-8ACA-45E4-91B1-7C12446777F7}"/>
     <hyperlink ref="O3" r:id="rId2" xr:uid="{0643A8C6-CEA2-46D4-9500-B4485B58464A}"/>
     <hyperlink ref="O6" r:id="rId3" xr:uid="{3F43E43A-3027-4A26-84D2-E6164C8EDD4F}"/>
+    <hyperlink ref="O5" r:id="rId4" xr:uid="{87407D3B-C853-4F42-AAAA-F2A4FF2A1E59}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait" r:id="rId4"/>
+  <pageSetup orientation="portrait" r:id="rId5"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
